--- a/out/Attention-Mamba1_repeat_2_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>7.999999562500022</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>7.999999562500022</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>7.999999562500022</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>7.999999562500022</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.04545455991735464</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_2_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>7.999999562500022</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.04545455991735464</v>
+        <v>2.021818185123966</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>7.999999562500022</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.04545455991735464</v>
+        <v>-0.01454544462809967</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>7.999999562500022</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.04545455991735464</v>
+        <v>-0.01454544462809967</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.01454544462809967</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5545454400826453</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>7.999999562500022</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.04545455991735464</v>
+        <v>1.003636370247934</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.04545455991735464</v>
+        <v>-0.01454544462809967</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.01454544462809967</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5545454400826453</v>
+        <v>-0.2145454446280997</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_2_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.004286956042051315</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.1199999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.003630198538303375</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.09000000000000027</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.005222771316766739</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.004422776401042938</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.006023485213518143</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.005770254880189896</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.004494965076446533</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.005428306758403778</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.006811141967773438</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.006532389670610428</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.006941951811313629</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.007023345679044724</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.007676370441913605</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0071534663438797</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.007213719189167023</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.004746217280626297</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.004615470767021179</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.003636370247934</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001340422779321671</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.003636370247934</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.00274541974067688</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.021818185123966</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.00193178653717041</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.003636370247934</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-4.098936915397644e-05</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.003636370247934</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.004169028252363205</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.01454544462809967</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.006405152380466461</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.004704650491476059</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.006502535194158554</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.005653664469718933</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.004662945866584778</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.006179060786962509</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.005547530949115753</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.004991393536329269</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.003636370247934</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.00282365083694458</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.003636370247934</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002198491245508194</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.003636370247934</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.002355616539716721</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.01454544462809967</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.004516609013080597</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.01454544462809967</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.005834653973579407</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.003904301673173904</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.005941726267337799</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.00606955960392952</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.005283746868371964</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.005375601351261139</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.005251478403806686</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.006278499960899353</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.006512507796287537</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.005581270903348923</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.006283290684223175</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.006072487682104111</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.005627427250146866</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.006212204694747925</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00579560175538063</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.006335541605949402</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.005677632987499237</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.005938384681940079</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.00594007596373558</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.005149073898792267</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.005674600601196289</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003652755171060562</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.004788350313901901</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0046723373234272</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.004679732024669647</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.005212947726249695</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.3</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.004693269729614258</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.00628168135881424</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.006213471293449402</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.00640256330370903</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.006710730493068695</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.005884405225515366</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.006108950823545456</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.006227511912584305</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.00576038658618927</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.005952831357717514</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.007284380495548248</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.006967131048440933</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0002892129123210907</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.003398623317480087</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.0001734420657157898</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.002728968858718872</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003454450517892838</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.005653325468301773</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.006193242967128754</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006134666502475739</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005730424076318741</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.004437372088432312</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.007183607667684555</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.005727216601371765</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.006138365715742111</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.007642030715942383</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.001529756933450699</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003479018807411194</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.004793900996446609</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006101943552494049</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.16</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005968216806650162</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.006643053144216537</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.007390055805444717</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.006046313792467117</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004978392273187637</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005802784115076065</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.006108436733484268</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.006115585565567017</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.007213715463876724</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.006259884685277939</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00515718013048172</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.00599130243062973</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.006255369633436203</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.005048070102930069</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.004689920693635941</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.3</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.006967920809984207</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.005840804427862167</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.00755072757601738</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.008527226746082306</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01045823097229004</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01151230931282043</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01179694384336472</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002799913287162781</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.009775102138519287</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.005803219974040985</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.006123863160610199</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.006058797240257263</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.005991317331790924</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01012090593576431</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.2145454446280997</v>
+        <v>0.3</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.009623829275369644</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.003636370247934</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0007249526679515839</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.003636370247934</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.0007392503321170807</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.003636370247934</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001067440956830978</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.01454544462809967</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005758922547101974</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.01454544462809967</v>
+        <v>0.4399999999999996</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01118115335702896</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.2145454446280997</v>
+        <v>-0.4400000000000003</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_2_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.004286956042051315</v>
+        <v>-0.004286967217922211</v>
       </c>
       <c r="JB2" t="n">
         <v>0.1199999999999997</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.003630198538303375</v>
+        <v>-0.003630168735980988</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.09000000000000027</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.005222771316766739</v>
+        <v>-0.005222763866186142</v>
       </c>
       <c r="JB4" t="n">
         <v>0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.006023485213518143</v>
+        <v>-0.006023459136486053</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.5799999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.004494965076446533</v>
+        <v>-0.004494968801736832</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.005428306758403778</v>
+        <v>-0.005428269505500793</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.006811141967773438</v>
+        <v>-0.006811168044805527</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.006532389670610428</v>
+        <v>-0.006532367318868637</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.8599999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.006941951811313629</v>
+        <v>-0.006941944360733032</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.007023345679044724</v>
+        <v>-0.007023308426141739</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.007676370441913605</v>
+        <v>-0.007676385343074799</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0071534663438797</v>
+        <v>-0.007153484970331192</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.007213719189167023</v>
+        <v>-0.007213708013296127</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.004615470767021179</v>
+        <v>-0.004615474492311478</v>
       </c>
       <c r="JB18" t="n">
         <v>0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.001340422779321671</v>
+        <v>0.00134040042757988</v>
       </c>
       <c r="JB19" t="n">
         <v>0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.00274541974067688</v>
+        <v>-0.002745408564805984</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.00193178653717041</v>
+        <v>0.001931816339492798</v>
       </c>
       <c r="JB21" t="n">
         <v>0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-4.098936915397644e-05</v>
+        <v>-4.103779792785645e-05</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.004169028252363205</v>
+        <v>-0.004169005900621414</v>
       </c>
       <c r="JB23" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.006405152380466461</v>
+        <v>-0.006405185908079147</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.004704650491476059</v>
+        <v>-0.00470464676618576</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.006502535194158554</v>
+        <v>-0.006502550095319748</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.005653664469718933</v>
+        <v>-0.005653649568557739</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.004662945866584778</v>
+        <v>-0.004662979394197464</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.8599999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.006179060786962509</v>
+        <v>-0.006179086863994598</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.005547530949115753</v>
+        <v>-0.00554753839969635</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.004991393536329269</v>
+        <v>-0.00499141588807106</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.00282365083694458</v>
+        <v>0.002823628485202789</v>
       </c>
       <c r="JB32" t="n">
         <v>0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.002198491245508194</v>
+        <v>-0.002198487520217896</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.004516609013080597</v>
+        <v>-0.004516627639532089</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.005834653973579407</v>
+        <v>-0.005834672600030899</v>
       </c>
       <c r="JB36" t="n">
         <v>0.16</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.003904301673173904</v>
+        <v>-0.003904290497303009</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.005941726267337799</v>
+        <v>-0.005941707640886307</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.00606955960392952</v>
+        <v>-0.006069522351026535</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.005283746868371964</v>
+        <v>-0.005283761769533157</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.005375601351261139</v>
+        <v>-0.005375619977712631</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.005251478403806686</v>
+        <v>-0.005251467227935791</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.006278499960899353</v>
+        <v>-0.006278514862060547</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.006512507796287537</v>
+        <v>-0.006512511521577835</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.006283290684223175</v>
+        <v>-0.006283294409513474</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.006072487682104111</v>
+        <v>-0.006072502583265305</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.005627427250146866</v>
+        <v>-0.005627453327178955</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.006212204694747925</v>
+        <v>-0.00621221587061882</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.00579560175538063</v>
+        <v>-0.005795609205961227</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.006335541605949402</v>
+        <v>-0.006335530430078506</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.005677632987499237</v>
+        <v>-0.005677603185176849</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.005938384681940079</v>
+        <v>-0.005938403308391571</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.2599999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.00594007596373558</v>
+        <v>-0.005940087139606476</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.2599999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.005149073898792267</v>
+        <v>-0.005149077624082565</v>
       </c>
       <c r="JB55" t="n">
         <v>0.02000000000000007</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.005674600601196289</v>
+        <v>-0.005674596875905991</v>
       </c>
       <c r="JB56" t="n">
         <v>0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.004788350313901901</v>
+        <v>-0.004788372665643692</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.0046723373234272</v>
+        <v>-0.004672326147556305</v>
       </c>
       <c r="JB59" t="n">
         <v>0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.004679732024669647</v>
+        <v>-0.004679717123508453</v>
       </c>
       <c r="JB60" t="n">
         <v>0.5799999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.005212947726249695</v>
+        <v>-0.005212973803281784</v>
       </c>
       <c r="JB61" t="n">
         <v>0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.004693269729614258</v>
+        <v>-0.004693273454904556</v>
       </c>
       <c r="JB62" t="n">
         <v>0.02000000000000007</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.006213471293449402</v>
+        <v>-0.006213463842868805</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.8599999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.00640256330370903</v>
+        <v>-0.006402555853128433</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.006710730493068695</v>
+        <v>-0.006710749119520187</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.005884405225515366</v>
+        <v>-0.005884416401386261</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.006108950823545456</v>
+        <v>-0.006108947098255157</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.8599999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.006227511912584305</v>
+        <v>-0.006227515637874603</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.8599999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.00576038658618927</v>
+        <v>-0.005760416388511658</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.005952831357717514</v>
+        <v>-0.005952827632427216</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.2599999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.007284380495548248</v>
+        <v>-0.007284391671419144</v>
       </c>
       <c r="JB72" t="n">
         <v>0.02000000000000007</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.006967131048440933</v>
+        <v>-0.006967112421989441</v>
       </c>
       <c r="JB73" t="n">
         <v>0.16</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.0002892129123210907</v>
+        <v>-0.0002892017364501953</v>
       </c>
       <c r="JB74" t="n">
         <v>0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.003398623317480087</v>
+        <v>-0.003398612141609192</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.0001734420657157898</v>
+        <v>-0.0001734271645545959</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.002728968858718872</v>
+        <v>-0.002728972584009171</v>
       </c>
       <c r="JB77" t="n">
         <v>0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003454450517892838</v>
+        <v>-0.003454416990280151</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.005653325468301773</v>
+        <v>-0.005653336644172668</v>
       </c>
       <c r="JB79" t="n">
         <v>0.16</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.006193242967128754</v>
+        <v>-0.006193261593580246</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.7199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.006134666502475739</v>
+        <v>-0.006134670227766037</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.8599999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.005730424076318741</v>
+        <v>-0.005730412900447845</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.8599999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.004437372088432312</v>
+        <v>-0.004437349736690521</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.007183607667684555</v>
+        <v>-0.007183592766523361</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.8599999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.005727216601371765</v>
+        <v>-0.005727209150791168</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.8599999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.006138365715742111</v>
+        <v>-0.006138347089290619</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.007642030715942383</v>
+        <v>-0.007642019540071487</v>
       </c>
       <c r="JB87" t="n">
         <v>0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.001529756933450699</v>
+        <v>-0.001529771834611893</v>
       </c>
       <c r="JB88" t="n">
         <v>0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.003479018807411194</v>
+        <v>-0.003479011356830597</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.004793900996446609</v>
+        <v>-0.004793882369995117</v>
       </c>
       <c r="JB90" t="n">
         <v>0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.006101943552494049</v>
+        <v>-0.006101951003074646</v>
       </c>
       <c r="JB91" t="n">
         <v>0.16</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.005968216806650162</v>
+        <v>-0.005968224257230759</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.1199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.007390055805444717</v>
+        <v>-0.007390029728412628</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.006046313792467117</v>
+        <v>-0.006046321243047714</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.004978392273187637</v>
+        <v>-0.004978399723768234</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.005802784115076065</v>
+        <v>-0.005802787840366364</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.006108436733484268</v>
+        <v>-0.006108447909355164</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.006115585565567017</v>
+        <v>-0.00611557811498642</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.007213715463876724</v>
+        <v>-0.007213734090328217</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.8599999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.006259884685277939</v>
+        <v>-0.006259888410568237</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.00515718013048172</v>
+        <v>-0.005157213658094406</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.8599999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.00599130243062973</v>
+        <v>-0.005991257727146149</v>
       </c>
       <c r="JB103" t="n">
         <v>0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.006255369633436203</v>
+        <v>-0.006255373358726501</v>
       </c>
       <c r="JB104" t="n">
         <v>0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.005048070102930069</v>
+        <v>-0.005048062652349472</v>
       </c>
       <c r="JB105" t="n">
         <v>0.1600000000000001</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.004689920693635941</v>
+        <v>-0.004689913243055344</v>
       </c>
       <c r="JB106" t="n">
         <v>0.3</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.006967920809984207</v>
+        <v>-0.006967980414628983</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.005840804427862167</v>
+        <v>-0.005840834230184555</v>
       </c>
       <c r="JB108" t="n">
         <v>0.02000000000000007</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.00755072757601738</v>
+        <v>-0.007550742477178574</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.2599999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.008527226746082306</v>
+        <v>-0.008527211844921112</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.8599999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.01045823097229004</v>
+        <v>-0.01045821234583855</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.01151230931282043</v>
+        <v>-0.01151233538985252</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.01179694384336472</v>
+        <v>-0.01179692149162292</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002799913287162781</v>
+        <v>-0.002799917012453079</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.009775102138519287</v>
+        <v>-0.009775120764970779</v>
       </c>
       <c r="JB115" t="n">
         <v>0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.005803219974040985</v>
+        <v>-0.005803227424621582</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.006123863160610199</v>
+        <v>-0.006123851984739304</v>
       </c>
       <c r="JB117" t="n">
         <v>0.5799999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.006058797240257263</v>
+        <v>-0.006058793514966965</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.005991317331790924</v>
+        <v>-0.005991328507661819</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.01012090593576431</v>
+        <v>-0.01012088358402252</v>
       </c>
       <c r="JB120" t="n">
         <v>0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.009623829275369644</v>
+        <v>-0.00962384045124054</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.0007249526679515839</v>
+        <v>0.0007249303162097931</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.0007392503321170807</v>
+        <v>-0.0007392466068267822</v>
       </c>
       <c r="JB123" t="n">
         <v>0.7199999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.001067440956830978</v>
+        <v>-0.001067444682121277</v>
       </c>
       <c r="JB124" t="n">
         <v>0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.005758922547101974</v>
+        <v>-0.005758941173553467</v>
       </c>
       <c r="JB125" t="n">
         <v>0.4399999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.01118115335702896</v>
+        <v>-0.01118117198348045</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.4400000000000003</v>
